--- a/Jack/jack_test_info.xlsx
+++ b/Jack/jack_test_info.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="17325" windowHeight="7155"/>
+    <workbookView windowWidth="27150" windowHeight="13365"/>
   </bookViews>
   <sheets>
-    <sheet name="9" sheetId="5" r:id="rId1"/>
-    <sheet name="7" sheetId="13" r:id="rId2"/>
-    <sheet name="8列炮" sheetId="3" r:id="rId3"/>
-    <sheet name="6" sheetId="6" r:id="rId4"/>
+    <sheet name="6" sheetId="6" r:id="rId1"/>
+    <sheet name="9" sheetId="5" r:id="rId2"/>
+    <sheet name="7" sheetId="13" r:id="rId3"/>
+    <sheet name="8列炮" sheetId="3" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="16" r:id="rId5"/>
     <sheet name="5" sheetId="4" r:id="rId6"/>
     <sheet name="3" sheetId="10" r:id="rId7"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="45">
   <si>
     <t>小丑类型</t>
   </si>
@@ -101,10 +101,10 @@
     <t>曾</t>
   </si>
   <si>
-    <t>非永动</t>
+    <t>永动</t>
   </si>
   <si>
-    <t>卡</t>
+    <t>炮</t>
   </si>
   <si>
     <t>被炸植物列数</t>
@@ -126,9 +126,6 @@
   </si>
   <si>
     <t>冰瓜额外溅射次数</t>
-  </si>
-  <si>
-    <t>永动</t>
   </si>
   <si>
     <t>测试次数</t>
@@ -155,10 +152,13 @@
     <t>锁植物攻击间隔</t>
   </si>
   <si>
-    <t>正炸</t>
+    <t>非永动</t>
   </si>
   <si>
-    <t>炮</t>
+    <t>卡</t>
+  </si>
+  <si>
+    <t>正炸</t>
   </si>
   <si>
     <t>全部</t>
@@ -167,13 +167,13 @@
     <t>前院</t>
   </si>
   <si>
-    <t>上炸下</t>
-  </si>
-  <si>
     <t>旗帜波</t>
   </si>
   <si>
     <t>最快</t>
+  </si>
+  <si>
+    <t>上炸下</t>
   </si>
   <si>
     <t>屋顶</t>
@@ -1350,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet7"/>
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:P25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
@@ -1438,7 +1438,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>18</v>
@@ -1447,21 +1447,21 @@
         <v>19</v>
       </c>
       <c r="G3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="3"/>
       <c r="K3" s="3"/>
       <c r="M3" s="6">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O3" s="6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P3" s="6">
-        <v>639</v>
+        <v>900</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1469,10 +1469,10 @@
         <v>21</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>18</v>
@@ -1481,7 +1481,7 @@
         <v>19</v>
       </c>
       <c r="G4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
@@ -1498,7 +1498,7 @@
         <v>23</v>
       </c>
       <c r="D5" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>18</v>
@@ -1507,7 +1507,7 @@
         <v>19</v>
       </c>
       <c r="G5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
@@ -1524,7 +1524,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>18</v>
@@ -1533,7 +1533,7 @@
         <v>19</v>
       </c>
       <c r="G6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
@@ -1542,9 +1542,9 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="4:16">
+    <row r="7" spans="1:16">
       <c r="D7" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>26</v>
@@ -1570,13 +1570,13 @@
         <v>0</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -1588,19 +1588,11 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="4:16">
-      <c r="D9" s="3">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
+    <row r="9" spans="1:16">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
       <c r="M9" s="6"/>
@@ -1610,10 +1602,10 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
-        <v>10000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1628,10 +1620,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -1644,7 +1636,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="4:16">
+    <row r="12" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1658,7 +1650,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -1676,7 +1668,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -1694,10 +1686,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1712,10 +1704,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1971,7 +1963,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3">
         <v>8</v>
@@ -1980,7 +1972,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -1993,7 +1985,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -2016,7 +2008,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -2042,7 +2034,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -2068,7 +2060,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -2080,7 +2072,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="4:16">
+    <row r="7" spans="1:16">
       <c r="D7" s="3">
         <v>5</v>
       </c>
@@ -2088,7 +2080,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -2114,7 +2106,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -2126,7 +2118,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="4:16">
+    <row r="9" spans="1:16">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -2140,7 +2132,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -2158,10 +2150,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -2174,7 +2166,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="4:16">
+    <row r="12" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -2188,7 +2180,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -2206,7 +2198,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -2224,10 +2216,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -2242,10 +2234,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -2501,7 +2493,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
@@ -2510,7 +2502,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -2523,7 +2515,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -2546,7 +2538,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -2563,7 +2555,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
@@ -2572,7 +2564,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -2598,7 +2590,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -2610,7 +2602,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="4:16">
+    <row r="7" spans="1:16">
       <c r="D7" s="3">
         <v>4</v>
       </c>
@@ -2618,7 +2610,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -2644,7 +2636,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -2656,7 +2648,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="4:16">
+    <row r="9" spans="1:16">
       <c r="D9" s="3">
         <v>2</v>
       </c>
@@ -2664,7 +2656,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -2678,7 +2670,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>1000000</v>
@@ -2696,10 +2688,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -2712,7 +2704,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="4:16">
+    <row r="12" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -2726,7 +2718,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -2744,7 +2736,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -2762,10 +2754,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -2780,10 +2772,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -3048,7 +3040,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
@@ -3061,7 +3053,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -3084,7 +3076,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G4" s="3">
         <v>1</v>
@@ -3110,7 +3102,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
@@ -3127,7 +3119,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="3">
         <v>6</v>
@@ -3136,7 +3128,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -3148,7 +3140,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="4:16">
+    <row r="7" spans="1:16">
       <c r="D7" s="3">
         <v>7</v>
       </c>
@@ -3156,7 +3148,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -3182,7 +3174,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -3194,7 +3186,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="4:16">
+    <row r="9" spans="1:16">
       <c r="D9" s="3">
         <v>5</v>
       </c>
@@ -3202,7 +3194,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -3216,7 +3208,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -3234,10 +3226,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -3250,7 +3242,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="4:16">
+    <row r="12" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -3264,7 +3256,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -3282,7 +3274,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -3300,10 +3292,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -3318,10 +3310,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -3586,7 +3578,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -3599,7 +3591,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -3622,7 +3614,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -3648,7 +3640,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
@@ -3674,7 +3666,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -3686,7 +3678,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="4:16">
+    <row r="7" spans="1:16">
       <c r="D7" s="3">
         <v>4</v>
       </c>
@@ -3694,7 +3686,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
         <v>1</v>
@@ -3720,7 +3712,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -3732,7 +3724,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="4:16">
+    <row r="9" spans="1:16">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -3746,7 +3738,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>500000</v>
@@ -3764,10 +3756,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -3780,7 +3772,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="4:16">
+    <row r="12" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -3794,7 +3786,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -3812,7 +3804,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -3830,10 +3822,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -3848,10 +3840,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -4116,7 +4108,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -4131,7 +4123,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -4154,7 +4146,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>1</v>
@@ -4180,7 +4172,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
@@ -4206,7 +4198,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -4218,7 +4210,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="4:16">
+    <row r="7" spans="1:16">
       <c r="D7" s="3">
         <v>7</v>
       </c>
@@ -4226,7 +4218,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -4252,7 +4244,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -4264,7 +4256,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="4:16">
+    <row r="9" spans="1:16">
       <c r="D9" s="3">
         <v>5</v>
       </c>
@@ -4272,7 +4264,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -4286,7 +4278,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>50000</v>
@@ -4298,7 +4290,7 @@
         <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
@@ -4312,10 +4304,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -4328,7 +4320,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="4:16">
+    <row r="12" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -4342,7 +4334,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -4360,7 +4352,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -4378,10 +4370,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4396,10 +4388,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -4569,6 +4561,542 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1:P25"/>
+  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.16666666666667" style="1"/>
+    <col min="4" max="6" width="8.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.16666666666667" style="1"/>
+    <col min="9" max="9" width="10" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.16666666666667" style="1"/>
+    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.16666666666667" style="1"/>
+    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
+    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="I1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="M2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="M3" s="6">
+        <v>600</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0</v>
+      </c>
+      <c r="P3" s="6">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3">
+        <v>7</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="D7" s="3">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="D9" s="3">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="3">
+        <v>10000000</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1400</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="4:16">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+    </row>
+    <row r="18" spans="4:16">
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+    </row>
+    <row r="19" spans="4:16">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+    </row>
+    <row r="20" spans="4:16">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+    </row>
+    <row r="21" spans="4:16">
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+    </row>
+    <row r="22" spans="4:16">
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+    </row>
+    <row r="23" spans="4:16">
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+    </row>
+    <row r="24" spans="4:16">
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+    </row>
+    <row r="25" spans="4:16">
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="K1:K2"/>
+  </mergeCells>
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
+      <formula1>"全部,早爆,晚爆"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+      <formula1>"前院,后院,屋顶"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
+      <formula1>"上炸下,下炸上,正炸"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 D3:D25">
+      <formula1>"1,2,3,4,5,6,7,8,9"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
+      <formula1>"南瓜,普通,炮"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6">
+      <formula1>"通常波,旗帜波"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B16">
+      <formula1>"随机,最快,最慢"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E25">
+      <formula1>"曾,喷"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
+      <formula1>"永动,非永动"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+      <formula1>"卡,炮"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:P25"/>
@@ -4655,7 +5183,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3">
         <v>9</v>
@@ -4664,7 +5192,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -4677,7 +5205,7 @@
         <v>1069</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -4700,7 +5228,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -4726,7 +5254,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -4752,7 +5280,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -4764,7 +5292,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="4:16">
+    <row r="7" spans="1:16">
       <c r="D7" s="3">
         <v>7</v>
       </c>
@@ -4772,7 +5300,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -4798,7 +5326,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -4810,7 +5338,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="4:16">
+    <row r="9" spans="1:16">
       <c r="D9" s="3">
         <v>4</v>
       </c>
@@ -4818,7 +5346,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -4832,7 +5360,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -4850,10 +5378,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -4866,7 +5394,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="4:16">
+    <row r="12" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -4880,7 +5408,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>1044</v>
@@ -4898,7 +5426,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -4916,10 +5444,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4934,10 +5462,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -5106,7 +5634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet48"/>
   <dimension ref="A1:P25"/>
@@ -5192,7 +5720,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3">
         <v>8</v>
@@ -5201,7 +5729,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -5214,7 +5742,7 @@
         <v>1048</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -5237,7 +5765,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -5254,7 +5782,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
@@ -5263,7 +5791,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -5289,7 +5817,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -5301,7 +5829,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="4:16">
+    <row r="7" spans="1:16">
       <c r="D7" s="3">
         <v>5</v>
       </c>
@@ -5309,7 +5837,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -5335,7 +5863,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -5347,7 +5875,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="4:16">
+    <row r="9" spans="1:16">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -5361,7 +5889,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>100000000</v>
@@ -5379,10 +5907,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5395,7 +5923,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="4:16">
+    <row r="12" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -5409,7 +5937,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -5427,7 +5955,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -5445,10 +5973,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5463,532 +5991,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
-  </mergeCells>
-  <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
-      <formula1>"全部,早爆,晚爆"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
-      <formula1>"前院,后院,屋顶"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
-      <formula1>"上炸下,下炸上,正炸"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 D3:D25">
-      <formula1>"1,2,3,4,5,6,7,8,9"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
-      <formula1>"南瓜,普通,炮"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6">
-      <formula1>"通常波,旗帜波"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B16">
-      <formula1>"随机,最快,最慢"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E25">
-      <formula1>"曾,喷"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
-      <formula1>"永动,非永动"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
-      <formula1>"卡,炮"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.16666666666667" style="1"/>
-    <col min="4" max="6" width="8.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="5.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.16666666666667" style="1"/>
-    <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="I1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="3">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="K3" s="3">
-        <v>300</v>
-      </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="3">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="3">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>3</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="4:16">
-      <c r="D7" s="3">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>8</v>
-      </c>
-      <c r="D8" s="3">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="4:16">
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="3">
-        <v>10000000</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="4:16">
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="3">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1400</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6244,7 +6250,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
@@ -6253,7 +6259,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -6281,7 +6287,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -6307,7 +6313,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -6333,7 +6339,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -6345,7 +6351,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" s="1" customFormat="1" spans="4:16">
+    <row r="7" s="1" customFormat="1" spans="1:16">
       <c r="D7" s="3">
         <v>6</v>
       </c>
@@ -6353,7 +6359,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
         <v>1</v>
@@ -6379,7 +6385,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -6391,7 +6397,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" s="1" customFormat="1" spans="4:16">
+    <row r="9" s="1" customFormat="1" spans="1:16">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -6405,7 +6411,7 @@
     </row>
     <row r="10" s="1" customFormat="1" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -6423,10 +6429,10 @@
     </row>
     <row r="11" s="1" customFormat="1" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6439,7 +6445,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" s="1" customFormat="1" spans="4:16">
+    <row r="12" s="1" customFormat="1" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -6453,7 +6459,7 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -6471,7 +6477,7 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -6489,10 +6495,10 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:16">
       <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6507,10 +6513,10 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6775,7 +6781,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
@@ -6788,7 +6794,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -6811,7 +6817,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -6837,7 +6843,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -6854,7 +6860,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -6863,7 +6869,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -6875,7 +6881,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="4:16">
+    <row r="7" spans="1:16">
       <c r="D7" s="3">
         <v>4</v>
       </c>
@@ -6883,7 +6889,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -6909,7 +6915,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -6921,7 +6927,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="4:16">
+    <row r="9" spans="1:16">
       <c r="D9" s="3">
         <v>2</v>
       </c>
@@ -6929,7 +6935,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -6943,7 +6949,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -6961,10 +6967,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6977,7 +6983,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="4:16">
+    <row r="12" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -6991,7 +6997,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -7009,7 +7015,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -7027,10 +7033,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -7045,10 +7051,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -7304,7 +7310,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
@@ -7313,7 +7319,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -7326,7 +7332,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -7349,7 +7355,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -7378,7 +7384,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -7404,7 +7410,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -7416,7 +7422,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="4:16">
+    <row r="7" spans="1:16">
       <c r="D7" s="3">
         <v>4</v>
       </c>
@@ -7424,7 +7430,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -7450,7 +7456,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -7462,7 +7468,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="4:16">
+    <row r="9" spans="1:16">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -7476,7 +7482,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -7494,10 +7500,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -7510,7 +7516,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="4:16">
+    <row r="12" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -7524,7 +7530,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -7542,7 +7548,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -7560,10 +7566,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -7578,10 +7584,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -7846,7 +7852,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -7861,7 +7867,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -7884,7 +7890,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -7910,7 +7916,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -7936,7 +7942,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -7948,7 +7954,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="4:16">
+    <row r="7" spans="1:16">
       <c r="D7" s="3">
         <v>5</v>
       </c>
@@ -7956,7 +7962,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -7982,7 +7988,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -7994,7 +8000,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="4:16">
+    <row r="9" spans="1:16">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -8008,7 +8014,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -8026,10 +8032,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -8042,7 +8048,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="4:16">
+    <row r="12" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -8056,7 +8062,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -8074,7 +8080,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -8092,10 +8098,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -8110,10 +8116,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -8378,7 +8384,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
@@ -8391,7 +8397,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -8414,7 +8420,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -8440,7 +8446,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -8466,7 +8472,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -8478,7 +8484,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="4:16">
+    <row r="7" spans="1:16">
       <c r="D7" s="3">
         <v>5</v>
       </c>
@@ -8486,7 +8492,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -8512,7 +8518,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -8524,7 +8530,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="4:16">
+    <row r="9" spans="1:16">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -8538,7 +8544,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>100000000</v>
@@ -8556,10 +8562,10 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -8572,7 +8578,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="4:16">
+    <row r="12" spans="1:16">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -8586,7 +8592,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -8604,7 +8610,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -8622,10 +8628,10 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -8640,10 +8646,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>

--- a/Jack/jack_test_info.xlsx
+++ b/Jack/jack_test_info.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27150" windowHeight="13365"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
-    <sheet name="6" sheetId="6" r:id="rId1"/>
-    <sheet name="9" sheetId="5" r:id="rId2"/>
-    <sheet name="7" sheetId="13" r:id="rId3"/>
+    <sheet name="7" sheetId="13" r:id="rId1"/>
+    <sheet name="6" sheetId="6" r:id="rId2"/>
+    <sheet name="9" sheetId="5" r:id="rId3"/>
     <sheet name="8列炮" sheetId="3" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="16" r:id="rId5"/>
     <sheet name="5" sheetId="4" r:id="rId6"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="47">
   <si>
     <t>小丑类型</t>
   </si>
@@ -95,25 +95,25 @@
     <t>被炸情况</t>
   </si>
   <si>
-    <t>下炸上</t>
+    <t>正炸</t>
   </si>
   <si>
     <t>曾</t>
   </si>
   <si>
-    <t>永动</t>
-  </si>
-  <si>
-    <t>炮</t>
+    <t>非永动</t>
   </si>
   <si>
     <t>被炸植物列数</t>
   </si>
   <si>
+    <t>永动</t>
+  </si>
+  <si>
     <t>被炸植物类型</t>
   </si>
   <si>
-    <t>普通</t>
+    <t>南瓜</t>
   </si>
   <si>
     <t>波次类型</t>
@@ -146,19 +146,31 @@
     <t>锁僵尸出生点与冻结倒计时</t>
   </si>
   <si>
-    <t>随机</t>
+    <t>最快</t>
   </si>
   <si>
     <t>锁植物攻击间隔</t>
   </si>
   <si>
-    <t>非永动</t>
+    <t>随机</t>
   </si>
   <si>
-    <t>卡</t>
+    <t>晚爆</t>
   </si>
   <si>
-    <t>正炸</t>
+    <t>上炸下</t>
+  </si>
+  <si>
+    <t>炮</t>
+  </si>
+  <si>
+    <t>下炸上</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>最慢</t>
   </si>
   <si>
     <t>全部</t>
@@ -168,12 +180,6 @@
   </si>
   <si>
     <t>旗帜波</t>
-  </si>
-  <si>
-    <t>最快</t>
-  </si>
-  <si>
-    <t>上炸下</t>
   </si>
   <si>
     <t>屋顶</t>
@@ -1350,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet5"/>
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:P25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
@@ -1438,7 +1444,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>18</v>
@@ -1449,27 +1455,21 @@
       <c r="G3" s="3">
         <v>0</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="3">
+        <v>12</v>
+      </c>
       <c r="K3" s="3"/>
-      <c r="M3" s="6">
-        <v>900</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
+      <c r="M3" s="6"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3">
         <v>5</v>
@@ -1478,7 +1478,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="D5" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -1524,13 +1524,13 @@
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -1544,7 +1544,7 @@
     </row>
     <row r="7" spans="1:16">
       <c r="D7" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>26</v>
@@ -1570,13 +1570,13 @@
         <v>0</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -1589,10 +1589,18 @@
       <c r="P8" s="6"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="D9" s="3">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
       <c r="M9" s="6"/>
@@ -1605,7 +1613,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="3">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1707,7 +1715,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1929,7 +1937,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -1963,7 +1971,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3">
         <v>8</v>
@@ -1972,7 +1980,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -1985,7 +1993,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -1996,7 +2004,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -2008,7 +2016,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -2025,7 +2033,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
@@ -2034,7 +2042,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -2060,7 +2068,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -2080,7 +2088,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -2106,7 +2114,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -2219,7 +2227,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -2237,7 +2245,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -2433,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -2493,7 +2501,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
@@ -2502,7 +2510,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -2515,7 +2523,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -2526,7 +2534,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -2538,7 +2546,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -2555,7 +2563,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
@@ -2564,7 +2572,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -2590,7 +2598,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -2610,7 +2618,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -2636,7 +2644,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -2656,7 +2664,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -2757,7 +2765,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -2775,7 +2783,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -3031,7 +3039,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3">
         <v>9</v>
@@ -3040,7 +3048,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
@@ -3053,7 +3061,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -3064,7 +3072,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>9</v>
@@ -3076,7 +3084,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>1</v>
@@ -3093,7 +3101,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3">
         <v>7</v>
@@ -3102,7 +3110,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
@@ -3119,7 +3127,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D6" s="3">
         <v>6</v>
@@ -3128,7 +3136,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -3148,7 +3156,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -3174,7 +3182,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -3194,7 +3202,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -3295,7 +3303,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -3313,7 +3321,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -3509,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -3569,7 +3577,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
@@ -3578,7 +3586,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -3591,7 +3599,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -3602,7 +3610,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -3614,7 +3622,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -3631,7 +3639,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
@@ -3640,7 +3648,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
@@ -3666,7 +3674,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -3686,7 +3694,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3">
         <v>1</v>
@@ -3712,7 +3720,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -3825,7 +3833,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -3843,7 +3851,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -4099,7 +4107,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3">
         <v>5</v>
@@ -4108,7 +4116,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -4123,7 +4131,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -4134,7 +4142,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>8</v>
@@ -4146,7 +4154,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>1</v>
@@ -4163,7 +4171,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3">
         <v>7</v>
@@ -4172,7 +4180,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
@@ -4198,7 +4206,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -4218,7 +4226,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -4244,7 +4252,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -4264,7 +4272,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -4290,7 +4298,7 @@
         <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
@@ -4373,7 +4381,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4391,7 +4399,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -4561,6 +4569,537 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:P25"/>
+  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.16666666666667" style="1"/>
+    <col min="4" max="6" width="8.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.16666666666667" style="1"/>
+    <col min="9" max="9" width="10" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.16666666666667" style="1"/>
+    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.16666666666667" style="1"/>
+    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
+    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="I1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="M2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>287</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="M3" s="6">
+        <f>2031-200+50</f>
+        <v>1881</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="6">
+        <v>100</v>
+      </c>
+      <c r="P3" s="6">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="3">
+        <v>10000000</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1400</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="4:16">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+    </row>
+    <row r="18" spans="4:16">
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+    </row>
+    <row r="19" spans="4:16">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+    </row>
+    <row r="20" spans="4:16">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+    </row>
+    <row r="21" spans="4:16">
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+    </row>
+    <row r="22" spans="4:16">
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+    </row>
+    <row r="23" spans="4:16">
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+    </row>
+    <row r="24" spans="4:16">
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+    </row>
+    <row r="25" spans="4:16">
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="K1:K2"/>
+  </mergeCells>
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
+      <formula1>"全部,早爆,晚爆"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+      <formula1>"前院,后院,屋顶"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
+      <formula1>"上炸下,下炸上,正炸"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 D3:D25">
+      <formula1>"1,2,3,4,5,6,7,8,9"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
+      <formula1>"南瓜,普通,炮"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6">
+      <formula1>"通常波,旗帜波"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B16">
+      <formula1>"随机,最快,最慢"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E25">
+      <formula1>"曾,喷"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
+      <formula1>"永动,非永动"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+      <formula1>"卡,炮"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:P25"/>
@@ -4647,7 +5186,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3">
         <v>9</v>
@@ -4656,29 +5195,25 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="M3" s="6">
-        <v>600</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
-      </c>
-      <c r="P3" s="6">
-        <v>639</v>
-      </c>
+      <c r="I3" s="3">
+        <v>440</v>
+      </c>
+      <c r="K3" s="3">
+        <v>161</v>
+      </c>
+      <c r="M3" s="6"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>9</v>
@@ -4690,7 +5225,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>1</v>
@@ -4707,7 +5242,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3">
         <v>7</v>
@@ -4716,10 +5251,10 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
@@ -4742,10 +5277,10 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
@@ -4762,7 +5297,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -4788,7 +5323,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -4808,7 +5343,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -4825,7 +5360,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="3">
-        <v>10000000</v>
+        <v>100000000</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -4909,7 +5444,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4927,545 +5462,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
-  </mergeCells>
-  <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
-      <formula1>"全部,早爆,晚爆"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
-      <formula1>"前院,后院,屋顶"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
-      <formula1>"上炸下,下炸上,正炸"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 D3:D25">
-      <formula1>"1,2,3,4,5,6,7,8,9"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
-      <formula1>"南瓜,普通,炮"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6">
-      <formula1>"通常波,旗帜波"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B16">
-      <formula1>"随机,最快,最慢"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E25">
-      <formula1>"曾,喷"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
-      <formula1>"永动,非永动"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
-      <formula1>"卡,炮"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:P25"/>
-  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.16666666666667" style="1"/>
-    <col min="4" max="6" width="8.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="5.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.16666666666667" style="1"/>
-    <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="I1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="3">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="M3" s="6">
-        <v>1069</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="3">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="3">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="D7" s="3">
-        <v>7</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>6</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="D9" s="3">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="3">
-        <v>10000000</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="3">
-        <v>1044</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1400</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -5720,7 +5717,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3">
         <v>8</v>
@@ -5729,7 +5726,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -5742,7 +5739,7 @@
         <v>1048</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -5753,7 +5750,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>8</v>
@@ -5765,7 +5762,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -5782,7 +5779,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
@@ -5791,7 +5788,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -5817,7 +5814,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -5837,7 +5834,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -5863,7 +5860,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -5976,7 +5973,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5994,7 +5991,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6190,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -6216,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -6250,7 +6247,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
@@ -6259,7 +6256,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -6275,7 +6272,7 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -6287,7 +6284,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -6304,7 +6301,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
@@ -6313,7 +6310,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -6339,7 +6336,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -6359,7 +6356,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3">
         <v>1</v>
@@ -6385,7 +6382,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -6498,7 +6495,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6516,7 +6513,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6712,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -6772,7 +6769,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
@@ -6781,7 +6778,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
@@ -6794,7 +6791,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -6805,7 +6802,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -6817,7 +6814,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -6834,7 +6831,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
@@ -6843,7 +6840,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -6860,7 +6857,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -6869,7 +6866,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -6889,7 +6886,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -6915,7 +6912,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -6935,7 +6932,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -7036,7 +7033,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -7054,7 +7051,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -7250,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -7276,7 +7273,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -7310,7 +7307,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
@@ -7319,7 +7316,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -7332,7 +7329,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -7343,7 +7340,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -7355,7 +7352,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -7375,7 +7372,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
@@ -7384,7 +7381,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -7410,7 +7407,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -7430,7 +7427,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -7456,7 +7453,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -7569,7 +7566,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -7587,7 +7584,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -7783,7 +7780,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -7809,7 +7806,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -7843,7 +7840,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3">
         <v>8</v>
@@ -7852,7 +7849,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -7867,7 +7864,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -7878,7 +7875,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -7890,7 +7887,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -7907,7 +7904,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
@@ -7916,7 +7913,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -7942,7 +7939,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -7962,7 +7959,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -7988,7 +7985,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -8101,7 +8098,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -8119,7 +8116,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -8375,7 +8372,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
@@ -8384,7 +8381,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
@@ -8397,7 +8394,7 @@
         <v>1039</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
@@ -8408,7 +8405,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -8420,7 +8417,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -8437,7 +8434,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
@@ -8446,7 +8443,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -8472,7 +8469,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -8492,7 +8489,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -8518,7 +8515,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -8631,7 +8628,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -8649,7 +8646,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>

--- a/Jack/jack_test_info.xlsx
+++ b/Jack/jack_test_info.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowHeight="8880"/>
   </bookViews>
   <sheets>
     <sheet name="7" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="48">
   <si>
     <t>小丑类型</t>
   </si>
@@ -55,8 +55,7 @@
 (升序)</t>
   </si>
   <si>
-    <t>冰瓜溅射时机列表
-(升序)</t>
+    <t>冰瓜溅射信息列表(时机升序)</t>
   </si>
   <si>
     <t>灰烬信息列表(时机升序)</t>
@@ -81,6 +80,9 @@
   </si>
   <si>
     <t>时机</t>
+  </si>
+  <si>
+    <t>伤害</t>
   </si>
   <si>
     <t>类型</t>
@@ -122,10 +124,10 @@
     <t>通常波</t>
   </si>
   <si>
-    <t>喷</t>
+    <t>已有伤害</t>
   </si>
   <si>
-    <t>冰瓜额外溅射次数</t>
+    <t>喷</t>
   </si>
   <si>
     <t>测试次数</t>
@@ -161,9 +163,6 @@
     <t>上炸下</t>
   </si>
   <si>
-    <t>炮</t>
-  </si>
-  <si>
     <t>下炸上</t>
   </si>
   <si>
@@ -171,6 +170,9 @@
   </si>
   <si>
     <t>最慢</t>
+  </si>
+  <si>
+    <t>炮</t>
   </si>
   <si>
     <t>全部</t>
@@ -1357,7 +1359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -1368,15 +1370,15 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1395,14 +1397,15 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1422,35 +1425,40 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3">
         <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -1459,14 +1467,15 @@
         <v>12</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="6"/>
+      <c r="L3" s="3"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
       <c r="P3" s="6"/>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -1475,142 +1484,150 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3">
         <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3">
         <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>100000000</v>
@@ -1621,17 +1638,18 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -1639,26 +1657,28 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -1669,14 +1689,15 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -1687,17 +1708,18 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1705,17 +1727,18 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1723,125 +1746,135 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -1875,7 +1908,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1887,7 +1920,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -1898,15 +1931,15 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1925,19 +1958,21 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -1952,35 +1987,41 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3">
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -1989,22 +2030,16 @@
         <v>585</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="M3" s="6">
-        <v>1039</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -2013,24 +2048,26 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>41</v>
@@ -2039,108 +2076,120 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -2151,17 +2200,19 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -2169,26 +2220,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -2199,14 +2254,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -2217,17 +2274,19 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -2235,17 +2294,19 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -2253,125 +2314,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -2405,7 +2486,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2417,7 +2498,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet14"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -2428,20 +2509,20 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -2455,14 +2536,16 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -2482,35 +2565,41 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -2519,22 +2608,16 @@
         <v>1</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="M3" s="6">
-        <v>1039</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -2543,142 +2626,156 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3">
         <v>2</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>1000000</v>
@@ -2689,17 +2786,19 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -2707,26 +2806,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -2737,14 +2840,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -2755,17 +2860,19 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -2773,17 +2880,19 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -2791,125 +2900,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -2943,7 +3072,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2955,7 +3084,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -2966,15 +3095,15 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2993,14 +3122,16 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -3020,23 +3151,29 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>40</v>
@@ -3045,34 +3182,26 @@
         <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
       </c>
       <c r="I3" s="3"/>
-      <c r="K3" s="3">
-        <v>307</v>
-      </c>
-      <c r="M3" s="6">
-        <v>1039</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>9</v>
@@ -3081,24 +3210,26 @@
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" s="3">
         <v>1</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>41</v>
@@ -3107,116 +3238,128 @@
         <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="3">
         <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3">
         <v>5</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -3227,17 +3370,19 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -3245,26 +3390,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -3275,14 +3424,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -3293,17 +3444,19 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -3311,17 +3464,19 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -3329,125 +3484,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -3481,7 +3656,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3493,7 +3668,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet34"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -3504,20 +3679,20 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -3531,14 +3706,16 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -3558,23 +3735,29 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>40</v>
@@ -3583,10 +3766,10 @@
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -3595,22 +3778,16 @@
         <v>800</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="M3" s="6">
-        <v>1039</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -3619,24 +3796,26 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>41</v>
@@ -3645,108 +3824,120 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3">
         <v>1</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>500000</v>
@@ -3757,17 +3948,19 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -3775,26 +3968,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -3805,14 +4002,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -3823,17 +4022,19 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -3841,17 +4042,19 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -3859,125 +4062,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -4011,7 +4234,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4023,7 +4246,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -4034,15 +4257,15 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4061,14 +4284,16 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -4088,23 +4313,29 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>40</v>
@@ -4113,10 +4344,10 @@
         <v>5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -4124,25 +4355,17 @@
       <c r="I3" s="3">
         <v>440</v>
       </c>
-      <c r="K3" s="3">
-        <v>50</v>
-      </c>
-      <c r="M3" s="6">
-        <v>1039</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>8</v>
@@ -4151,24 +4374,26 @@
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>1</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>41</v>
@@ -4177,116 +4402,128 @@
         <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>7</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>3</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3">
         <v>5</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>50000</v>
@@ -4295,27 +4532,29 @@
         <v>4</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -4323,26 +4562,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -4353,14 +4596,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -4371,17 +4616,19 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4389,17 +4636,19 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -4407,125 +4656,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -4559,7 +4828,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4571,7 +4840,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -4582,20 +4851,20 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -4609,14 +4878,16 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -4636,35 +4907,41 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -4673,23 +4950,16 @@
         <v>287</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="M3" s="6">
-        <f>2031-200+50</f>
-        <v>1881</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -4698,134 +4968,148 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>3</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -4836,17 +5120,19 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -4854,26 +5140,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -4884,14 +5174,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -4902,17 +5194,19 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4920,17 +5214,19 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -4938,125 +5234,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -5090,7 +5406,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5102,7 +5418,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -5113,15 +5429,15 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5140,14 +5456,16 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -5167,23 +5485,29 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>40</v>
@@ -5192,10 +5516,10 @@
         <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
@@ -5203,17 +5527,17 @@
       <c r="I3" s="3">
         <v>440</v>
       </c>
-      <c r="K3" s="3">
-        <v>161</v>
-      </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="6"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
       <c r="P3" s="6"/>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>9</v>
@@ -5222,24 +5546,26 @@
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>1</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>41</v>
@@ -5248,116 +5574,128 @@
         <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3">
         <v>5</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>100000000</v>
@@ -5368,17 +5706,19 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5386,26 +5726,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -5416,14 +5760,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -5434,14 +5780,16 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>42</v>
@@ -5452,14 +5800,16 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>42</v>
@@ -5470,125 +5820,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -5622,7 +5992,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5634,7 +6004,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet48"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -5645,14 +6015,15 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5671,14 +6042,16 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -5698,35 +6071,41 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3">
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -5735,22 +6114,16 @@
         <v>1</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="M3" s="6">
-        <v>1048</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>8</v>
@@ -5759,134 +6132,148 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D5" s="3">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>100000000</v>
@@ -5897,17 +6284,19 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5915,26 +6304,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -5945,14 +6338,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -5963,17 +6358,19 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5981,17 +6378,19 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -5999,125 +6398,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -6151,7 +6570,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6163,7 +6582,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -6174,20 +6593,20 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16">
+    <row r="1" s="1" customFormat="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -6201,19 +6620,21 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -6228,51 +6649,57 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:17">
+      <c r="A4" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="K3" s="3">
-        <v>300</v>
-      </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:16">
-      <c r="A4" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -6281,24 +6708,26 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>41</v>
@@ -6307,108 +6736,120 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3">
         <v>1</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>5</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:17">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -6419,17 +6860,19 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6437,26 +6880,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -6467,14 +6914,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -6485,17 +6934,19 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6503,17 +6954,19 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6521,125 +6974,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -6673,7 +7146,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6685,7 +7158,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet25"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -6696,20 +7169,20 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -6723,14 +7196,16 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -6750,23 +7225,29 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>40</v>
@@ -6775,10 +7256,10 @@
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
@@ -6787,22 +7268,16 @@
         <v>901</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="M3" s="6">
-        <v>1039</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -6811,24 +7286,26 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>41</v>
@@ -6837,116 +7314,128 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3">
         <v>2</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -6957,17 +7446,19 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6975,26 +7466,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -7005,14 +7500,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -7023,17 +7520,19 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -7041,17 +7540,19 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -7059,125 +7560,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -7211,7 +7732,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7223,7 +7744,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -7234,20 +7755,20 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -7261,19 +7782,21 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -7288,35 +7811,41 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -7325,22 +7854,16 @@
         <v>830</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="M3" s="6">
-        <v>1039</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -7349,10 +7872,10 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -7362,14 +7885,16 @@
         <v>3331</v>
       </c>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>41</v>
@@ -7378,108 +7903,120 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -7490,17 +8027,19 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -7508,26 +8047,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -7538,14 +8081,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -7556,17 +8101,19 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -7574,17 +8121,19 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -7592,125 +8141,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -7744,7 +8313,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7756,7 +8325,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet12"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -7767,20 +8336,20 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -7794,19 +8363,21 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -7821,23 +8392,29 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>40</v>
@@ -7846,10 +8423,10 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -7857,25 +8434,17 @@
       <c r="I3" s="3">
         <v>300</v>
       </c>
-      <c r="K3" s="3">
-        <v>200</v>
-      </c>
-      <c r="M3" s="6">
-        <v>1039</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -7884,24 +8453,26 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>41</v>
@@ -7910,108 +8481,120 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>10000000</v>
@@ -8022,17 +8605,19 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -8040,26 +8625,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -8070,14 +8659,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -8088,17 +8679,19 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -8106,17 +8699,19 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -8124,125 +8719,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -8276,7 +8891,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8288,7 +8903,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
@@ -8299,15 +8914,15 @@
     <col min="8" max="8" width="9.16666666666667" style="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.16666666666667" style="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.16666666666667" style="1"/>
-    <col min="13" max="13" width="5.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.16666666666667" style="1"/>
+    <col min="11" max="12" width="12.5916666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.16666666666667" style="1"/>
+    <col min="14" max="14" width="5.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8326,14 +8941,16 @@
       <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -8353,23 +8970,29 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>40</v>
@@ -8378,10 +9001,10 @@
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
@@ -8390,22 +9013,16 @@
         <v>783</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="M3" s="6">
-        <v>1039</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="6">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="L3" s="3"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -8414,24 +9031,26 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="6"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>41</v>
@@ -8440,108 +9059,120 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="6"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="3">
         <v>5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="D8" s="3">
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3"/>
       <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8" s="6"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3"/>
       <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" s="6"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>100000000</v>
@@ -8552,17 +9183,19 @@
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -8570,26 +9203,30 @@
       <c r="G11" s="3"/>
       <c r="I11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" s="6"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" s="6"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
@@ -8600,14 +9237,16 @@
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
       <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" s="6"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2">
         <v>1400</v>
@@ -8618,17 +9257,19 @@
       <c r="G14" s="3"/>
       <c r="I14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3"/>
       <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="6"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -8636,17 +9277,19 @@
       <c r="G15" s="3"/>
       <c r="I15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15" s="6"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -8654,125 +9297,145 @@
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="6"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="4:16">
+      <c r="Q16" s="6"/>
+    </row>
+    <row r="17" spans="4:17">
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="6"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="4:16">
+      <c r="Q17" s="6"/>
+    </row>
+    <row r="18" spans="4:17">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="6"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="4:16">
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="4:17">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="6"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="4:16">
+      <c r="Q19" s="6"/>
+    </row>
+    <row r="20" spans="4:17">
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="6"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3"/>
       <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="4:16">
+      <c r="Q20" s="6"/>
+    </row>
+    <row r="21" spans="4:17">
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="6"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3"/>
       <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="4:16">
+      <c r="Q21" s="6"/>
+    </row>
+    <row r="22" spans="4:17">
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="6"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="4:16">
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="4:17">
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="6"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="4:16">
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="4:17">
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="6"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="4:16">
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="4:17">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="6"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
@@ -8806,7 +9469,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F25">
       <formula1>"永动,非永动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O25">
       <formula1>"卡,炮"</formula1>
     </dataValidation>
   </dataValidations>
